--- a/artfynd/A 11692-2025 artfynd.xlsx
+++ b/artfynd/A 11692-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113566867</v>
+        <v>113566866</v>
       </c>
       <c r="B2" t="n">
-        <v>8403</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>44177</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>101735</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>452724</v>
+        <v>452728</v>
       </c>
       <c r="R2" t="n">
-        <v>6508473</v>
+        <v>6508455</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113566866</v>
+        <v>113566867</v>
       </c>
       <c r="B3" t="n">
-        <v>43639</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101735</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>452728</v>
+        <v>452724</v>
       </c>
       <c r="R3" t="n">
-        <v>6508455</v>
+        <v>6508473</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
